--- a/Fase 3/Evidencias del Proyecto/Presupuesto proyecto IncluShop.xlsx
+++ b/Fase 3/Evidencias del Proyecto/Presupuesto proyecto IncluShop.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benlu\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FelipeMunhoz18-Bravo-Vargas-Munoz-Docs\Fase 3\Evidencias del Proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8794AB54-3F3B-412C-92F8-D81D7C369948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{250B0480-917C-43EF-B6B6-68F1465E34F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C9B0B423-4A3A-4590-9382-24C0D8B6837F}"/>
   </bookViews>
@@ -398,7 +398,7 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -447,9 +447,6 @@
     </xf>
     <xf numFmtId="41" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -767,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E17C452-4C71-4BC4-95A6-D021236F6BDA}">
-  <dimension ref="C3:C17"/>
+  <dimension ref="C3:C12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="118" style="19" customWidth="1"/>
@@ -803,21 +800,6 @@
       <c r="C11" s="21"/>
     </row>
     <row r="12" spans="3:3" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C13" s="29"/>
-    </row>
-    <row r="14" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C14" s="29"/>
-    </row>
-    <row r="15" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C15" s="29"/>
-    </row>
-    <row r="16" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C16" s="29"/>
-    </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C17" s="29"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -836,7 +818,9 @@
     <col min="5" max="7" width="11.44140625" style="1"/>
     <col min="8" max="8" width="13.88671875" style="1" customWidth="1"/>
     <col min="9" max="14" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
